--- a/output/pdf_financials_xlsx/PNGC.xlsx
+++ b/output/pdf_financials_xlsx/PNGC.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="24">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="30">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5228,10 +5228,10 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>2.500494</v>
+        <v>-2.500494</v>
       </c>
     </row>
     <row r="83">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.315608</v>
+        <v>-0.315608</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.301249</v>
+        <v>-0.301249</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/PNGC.xlsx
+++ b/output/pdf_financials_xlsx/PNGC.xlsx
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008189999999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.007512</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.037811</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008189999999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.007512</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.037811</v>
       </c>
     </row>
     <row r="37">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/PNGC.xlsx
+++ b/output/pdf_financials_xlsx/PNGC.xlsx
@@ -3475,7 +3475,11 @@
           <t>Common shares issued for cash (note 5)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
